--- a/artfynd/A 43910-2024 artfynd.xlsx
+++ b/artfynd/A 43910-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89564760</v>
+        <v>89564738</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>399205.2019433596</v>
+        <v>398966</v>
       </c>
       <c r="R2" t="n">
-        <v>7085127.214150251</v>
+        <v>7085007</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89564789</v>
+        <v>89564775</v>
       </c>
       <c r="B3" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>398918.8081791264</v>
+        <v>399014</v>
       </c>
       <c r="R3" t="n">
-        <v>7085050.886528517</v>
+        <v>7085489</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89564774</v>
+        <v>89564754</v>
       </c>
       <c r="B4" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>398915.1223209504</v>
+        <v>399005</v>
       </c>
       <c r="R4" t="n">
-        <v>7085059.825608002</v>
+        <v>7085542</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,21 +945,11 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-08-02</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1003,6 +958,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1023,37 +983,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89564754</v>
+        <v>89564750</v>
       </c>
       <c r="B5" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1018,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>399004.8539152063</v>
+        <v>399047</v>
       </c>
       <c r="R5" t="n">
-        <v>7085542.002216325</v>
+        <v>7085566</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,21 +1051,11 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-08-02</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1119,11 +1064,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1144,15 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89564750</v>
+        <v>89564774</v>
       </c>
       <c r="B6" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,10 +1119,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>399047.1365858176</v>
+        <v>398915</v>
       </c>
       <c r="R6" t="n">
-        <v>7085566.213614567</v>
+        <v>7085060</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,19 +1152,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,37 +1185,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89564775</v>
+        <v>89564782</v>
       </c>
       <c r="B7" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>399014.1763141361</v>
+        <v>398761</v>
       </c>
       <c r="R7" t="n">
-        <v>7085488.788534806</v>
+        <v>7085326</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,19 +1253,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,15 +1286,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89564738</v>
+        <v>89564789</v>
       </c>
       <c r="B8" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,21 +1297,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1416,10 +1321,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>398965.9682096078</v>
+        <v>398919</v>
       </c>
       <c r="R8" t="n">
-        <v>7085007.028295272</v>
+        <v>7085051</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1449,19 +1354,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,15 +1387,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89564798</v>
+        <v>89564745</v>
       </c>
       <c r="B9" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,34 +1398,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tjaajatjaeltjie, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>399189.9097485368</v>
+        <v>399153</v>
       </c>
       <c r="R9" t="n">
-        <v>7085091.103346778</v>
+        <v>7085597</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1565,19 +1459,14 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-08-02</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,12 +1500,7 @@
         <v>89564726</v>
       </c>
       <c r="B10" t="n">
-        <v>78533</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80398</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,10 +1532,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>399152.145475115</v>
+        <v>399152</v>
       </c>
       <c r="R10" t="n">
-        <v>7085605.16061007</v>
+        <v>7085605</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,19 +1565,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,131 +1596,6 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>89564745</v>
-      </c>
-      <c r="B11" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Tjaajatjaeltjie, Jmt</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>399153.213363746</v>
-      </c>
-      <c r="R11" t="n">
-        <v>7085597.189501964</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Kall</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2020-07-01</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>

--- a/artfynd/A 43910-2024 artfynd.xlsx
+++ b/artfynd/A 43910-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564738</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564775</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564754</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564750</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564774</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564782</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1382,6 +1417,11 @@
       <c r="AY8" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564789</t>
         </is>
       </c>
     </row>
@@ -1494,6 +1534,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564745</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1600,8 +1645,24 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564726</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>